--- a/data/directmarketlogins.xlsx
+++ b/data/directmarketlogins.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBS NL62\PycharmProjects\PythonProject\data\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBS NL62\PycharmProjects\PythonProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1BEB0E-DA72-4C1B-97F8-34D72998607B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A55669-1E7E-4CA3-BAB3-B28FA52F4CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{19DC07F2-E79B-4B61-93A4-EE7197C63A8E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t xml:space="preserve">Market  </t>
   </si>
@@ -479,9 +479,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C817E1BB-235A-4A9D-890A-E36F7FB0A2F9}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -587,45 +588,12 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -636,9 +604,142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B701B4F-3345-496E-A238-744101EDB68F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>